--- a/input/ES/alignment_targets_retirement.xlsx
+++ b/input/ES/alignment_targets_retirement.xlsx
@@ -85,7 +85,7 @@
     <t>Produced</t>
   </si>
   <si>
-    <t>11 Aug 2026</t>
+    <t>26 Sep 2026</t>
   </si>
 </sst>
 </file>
@@ -539,7 +539,7 @@
         <v>2011</v>
       </c>
       <c r="B2" s="14">
-        <v>0.16098815202713013</v>
+        <v>0.16098836064338684</v>
       </c>
     </row>
     <row r="3">
@@ -547,7 +547,7 @@
         <v>2012</v>
       </c>
       <c r="B3" s="15">
-        <v>0.16354553401470184</v>
+        <v>0.1635458767414093</v>
       </c>
     </row>
     <row r="4">
@@ -555,7 +555,7 @@
         <v>2013</v>
       </c>
       <c r="B4" s="16">
-        <v>0.16562020778656006</v>
+        <v>0.16562037169933319</v>
       </c>
     </row>
     <row r="5">
@@ -563,7 +563,7 @@
         <v>2014</v>
       </c>
       <c r="B5" s="17">
-        <v>0.16772221028804779</v>
+        <v>0.16772212088108063</v>
       </c>
     </row>
     <row r="6">
@@ -571,7 +571,7 @@
         <v>2015</v>
       </c>
       <c r="B6" s="18">
-        <v>0.16929870843887329</v>
+        <v>0.16930186748504639</v>
       </c>
     </row>
     <row r="7">
@@ -579,7 +579,7 @@
         <v>2016</v>
       </c>
       <c r="B7" s="19">
-        <v>0.173662930727005</v>
+        <v>0.17366282641887665</v>
       </c>
     </row>
     <row r="8">
@@ -587,7 +587,7 @@
         <v>2017</v>
       </c>
       <c r="B8" s="20">
-        <v>0.18029135465621948</v>
+        <v>0.18029128015041351</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         <v>2018</v>
       </c>
       <c r="B9" s="21">
-        <v>0.18751123547554016</v>
+        <v>0.18751136958599091</v>
       </c>
     </row>
     <row r="10">
@@ -603,7 +603,7 @@
         <v>2019</v>
       </c>
       <c r="B10" s="22">
-        <v>0.18977364897727966</v>
+        <v>0.18977363407611847</v>
       </c>
     </row>
     <row r="11">
@@ -611,7 +611,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="23">
-        <v>0.16699975728988647</v>
+        <v>0.16699901223182678</v>
       </c>
     </row>
     <row r="12">
@@ -619,7 +619,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="24">
-        <v>0.18759851157665253</v>
+        <v>0.18759846687316895</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="25">
-        <v>0.18866083025932312</v>
+        <v>0.18866066634654999</v>
       </c>
     </row>
     <row r="14">
@@ -635,7 +635,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="26">
-        <v>0.18745963275432587</v>
+        <v>0.18745972216129303</v>
       </c>
     </row>
   </sheetData>
